--- a/marketing_report/outputs/Embudo_Conversion/Embudo_Conversion_Datos.xlsx
+++ b/marketing_report/outputs/Embudo_Conversion/Embudo_Conversion_Datos.xlsx
@@ -499,37 +499,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>61452</v>
+        <v>63966</v>
       </c>
       <c r="C2" t="n">
-        <v>2252</v>
+        <v>2479</v>
       </c>
       <c r="D2" t="n">
-        <v>3.66464883160841</v>
+        <v>3.87549635743989</v>
       </c>
       <c r="E2" t="n">
         <v>7704</v>
       </c>
       <c r="F2" t="n">
-        <v>297</v>
+        <v>444</v>
       </c>
       <c r="G2" t="n">
-        <v>7407</v>
+        <v>7260</v>
       </c>
       <c r="H2" t="n">
-        <v>3.855140186915888</v>
+        <v>5.763239875389408</v>
       </c>
       <c r="I2" t="n">
-        <v>4789</v>
+        <v>5547</v>
       </c>
       <c r="J2" t="n">
-        <v>7.793074269348435</v>
+        <v>8.671794390770096</v>
       </c>
       <c r="K2" t="n">
-        <v>5452</v>
+        <v>5225</v>
       </c>
       <c r="L2" t="n">
-        <v>4029</v>
+        <v>4042</v>
       </c>
     </row>
     <row r="3">
@@ -539,37 +539,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>334</v>
+        <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1.796407185628742</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>374</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="H3" t="n">
-        <v>1.336898395721925</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>324</v>
+        <v>10</v>
       </c>
       <c r="J3" t="n">
-        <v>97.0059880239521</v>
+        <v>90.90909090909091</v>
       </c>
       <c r="K3" t="n">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="L3" t="n">
-        <v>557</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4">
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -600,16 +600,16 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J4" t="n">
-        <v>80</v>
+        <v>80.85106382978722</v>
       </c>
       <c r="K4" t="n">
         <v>136</v>
       </c>
       <c r="L4" t="n">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
   </sheetData>
@@ -680,22 +680,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21417</v>
+        <v>21570</v>
       </c>
       <c r="D2" t="n">
-        <v>473</v>
+        <v>505</v>
       </c>
       <c r="E2" t="n">
-        <v>2.208525937339497</v>
+        <v>2.34121464997682</v>
       </c>
       <c r="F2" t="n">
-        <v>538</v>
+        <v>579</v>
       </c>
       <c r="G2" t="n">
-        <v>2.51202315917262</v>
+        <v>2.684283727399166</v>
       </c>
       <c r="H2" t="n">
-        <v>113.7420718816068</v>
+        <v>114.6534653465346</v>
       </c>
     </row>
     <row r="3">
@@ -710,22 +710,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12220</v>
+        <v>13028</v>
       </c>
       <c r="D3" t="n">
-        <v>362</v>
+        <v>391</v>
       </c>
       <c r="E3" t="n">
-        <v>2.962356792144026</v>
+        <v>3.001228124040528</v>
       </c>
       <c r="F3" t="n">
-        <v>284</v>
+        <v>338</v>
       </c>
       <c r="G3" t="n">
-        <v>2.324058919803601</v>
+        <v>2.594412035615597</v>
       </c>
       <c r="H3" t="n">
-        <v>78.45303867403315</v>
+        <v>86.44501278772378</v>
       </c>
     </row>
     <row r="4">
@@ -740,22 +740,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>822</v>
+        <v>968</v>
       </c>
       <c r="D4" t="n">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="E4" t="n">
-        <v>13.5036496350365</v>
+        <v>13.84297520661157</v>
       </c>
       <c r="F4" t="n">
-        <v>222</v>
+        <v>267</v>
       </c>
       <c r="G4" t="n">
-        <v>27.00729927007299</v>
+        <v>27.58264462809917</v>
       </c>
       <c r="H4" t="n">
-        <v>200</v>
+        <v>199.2537313432836</v>
       </c>
     </row>
     <row r="5">
@@ -770,22 +770,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>26993</v>
+        <v>28400</v>
       </c>
       <c r="D5" t="n">
-        <v>1306</v>
+        <v>1449</v>
       </c>
       <c r="E5" t="n">
-        <v>4.838291408883785</v>
+        <v>5.102112676056338</v>
       </c>
       <c r="F5" t="n">
-        <v>3745</v>
+        <v>4363</v>
       </c>
       <c r="G5" t="n">
-        <v>13.873967324862</v>
+        <v>15.36267605633803</v>
       </c>
       <c r="H5" t="n">
-        <v>286.7534456355284</v>
+        <v>301.104209799862</v>
       </c>
     </row>
     <row r="6">
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -809,10 +809,10 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -830,22 +830,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
         <v>2</v>
-      </c>
-      <c r="E7" t="n">
-        <v>5.88235294117647</v>
-      </c>
-      <c r="F7" t="n">
-        <v>34</v>
       </c>
       <c r="G7" t="n">
         <v>100</v>
       </c>
       <c r="H7" t="n">
-        <v>1700</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -869,10 +869,10 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -890,22 +890,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>270</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>1.481481481481482</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>265</v>
+        <v>7</v>
       </c>
       <c r="G9" t="n">
-        <v>98.14814814814815</v>
+        <v>87.5</v>
       </c>
       <c r="H9" t="n">
-        <v>6625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -920,19 +920,19 @@
         </is>
       </c>
       <c r="C10" t="n">
+        <v>8</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
         <v>6</v>
       </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>4</v>
-      </c>
       <c r="G10" t="n">
-        <v>66.66666666666666</v>
+        <v>75</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1096,22 +1096,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>20372</v>
+        <v>22997</v>
       </c>
       <c r="D2" t="n">
-        <v>1826</v>
+        <v>2068</v>
       </c>
       <c r="E2" t="n">
-        <v>8.96328293736501</v>
+        <v>8.99247727964517</v>
       </c>
       <c r="F2" t="n">
-        <v>3934</v>
+        <v>4700</v>
       </c>
       <c r="G2" t="n">
-        <v>19.31081877086197</v>
+        <v>20.43744836282994</v>
       </c>
       <c r="H2" t="n">
-        <v>215.4435925520263</v>
+        <v>227.2727272727273</v>
       </c>
     </row>
     <row r="3">
@@ -1126,22 +1126,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>41080</v>
+        <v>40969</v>
       </c>
       <c r="D3" t="n">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="E3" t="n">
-        <v>1.037000973709834</v>
+        <v>1.003197539603115</v>
       </c>
       <c r="F3" t="n">
-        <v>855</v>
+        <v>847</v>
       </c>
       <c r="G3" t="n">
-        <v>2.081304771178189</v>
+        <v>2.06741682735727</v>
       </c>
       <c r="H3" t="n">
-        <v>200.7042253521127</v>
+        <v>206.0827250608272</v>
       </c>
     </row>
     <row r="4">
@@ -1156,7 +1156,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>63</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -1165,10 +1165,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>92.06349206349206</v>
+        <v>100</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -1186,22 +1186,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>271</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>2.214022140221402</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>266</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>98.1549815498155</v>
+        <v>87.5</v>
       </c>
       <c r="H5" t="n">
-        <v>4433.333333333334</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -1255,10 +1255,10 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G7" t="n">
-        <v>76</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
